--- a/L1-BLANKS-REGISTER.xlsx
+++ b/L1-BLANKS-REGISTER.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -500,78 +500,40 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>BLANK-23</t>
+          <t>BLANK-25</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>L1-01 §23 vs L1-14</t>
+          <t>L1-01 §25 Vocabulary</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>FINANCIAL invariant ID collision. L1-01 §23 assigns F-03 = Governance Determinism and F-04 = Waterfall Determinism. L1-14 assigns F-03 = Distributions Follow Waterfall and F-04 = Reserve Floor Enforced. Two documents give the same IDs to different rules. Violates §14 Naming Authority.</t>
+          <t>Should "Consumer" join the forbidden term list? It appears 6 times in GC.SYSTEM v3.0. Currently only Customer and User are forbidden, so the linter passes Consumer.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>PROPOSED: adopt the L1-14 numbering as canonical (it is the dedicated invariant register) and renumber L1-01 §23. Also fold in the 4 new invariants from L1-16 (F-10 Revenue Base Determinism, F-11 Capital Call Purpose Gate, F-12 Reserve Non-Pooling, F-13 Brand Participation Is Not Equity). Net result: one FINANCIAL invariant table, 13 entries. MUST be fixed before any F-invariant reaches code.</t>
+          <t>PROPOSED: add it. Same family and same error as Customer - it frames a Member as someone who consumes rather than someone who owns. Adding it is a constitutional vocabulary amendment under §25 and is not mine to make unilaterally. One word closes this.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>L5, L10, all F-invariants</t>
+          <t>L8 UX, brand surface</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Enterprise Architecture</t>
+          <t>Knowledge Office</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>BLANK-09a</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>L1-16 §2.6</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Reserve breach response - does the distribution suspension survive? Instruction was "just a broadcast is sent and expenses are delayed". The BLANK-09 ruling had explicitly said discretionary distributions ARE suspended. The later instruction did not say to remove it.</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>IMPLEMENTED CONSERVATIVELY: suspension RETAINED alongside broadcast + expenditure deferral. If distributions should continue during a breach, say so - but note that partner distributions continuing while the reserve is below floor materially weakens invariant F-04. One-line confirmation closes this.</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>F-04, L5</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Finance</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -584,7 +546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -855,7 +817,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>RATIFIED - NOT NAV-linked. Dual reserve funded from Revenue Base: 2.5% Enterprise Administration Reserve + 2.5% Property Sinking Fund, transferred before partner distributions. Floor = greater of (6 months non-operational fixed obligations) or (Board-approved AAMP minimum). OpCo day-to-day opex EXCLUDED. Per-LLP, non-pooled. Bands: &gt;=120 healthy / 110-119 advisory / 100-109 governance alert / &lt;100 constitutional breach. BREACH RESPONSE AMENDED 30 Jul: broadcast notification + discretionary expenditure deferred + discretionary distributions suspended. The 5/15/30-day Board escalation machinery is REPEALED - a reserve breach is a known condition with a known remedy and does not need a bespoke Board process each time. A reserve breach shall NEVER trigger a capital call. Post-stabilisation capital calls are GROWTH capital only - never operating deficits, routine maintenance, or reserve replenishment.</t>
+          <t>RATIFIED - NOT NAV-linked. Dual reserve funded from Revenue Base: 2.5% Enterprise Administration Reserve + 2.5% Property Sinking Fund, transferred before partner distributions. Floor = greater of (6 months non-operational fixed obligations) or (Board-approved AAMP minimum). OpCo day-to-day opex EXCLUDED. Per-LLP, non-pooled. Bands: &gt;=120 healthy / 110-119 advisory / 100-109 governance alert / &lt;100 constitutional breach. BREACH RESPONSE (final, see BLANK-09a): AUTOMATIC = broadcast notification + discretionary expenditure deferred. BY RESOLUTION ONLY = suspension of distributions, which needs both an active breach AND an Ordinary Resolution. The 5/15/30-day Board escalation machinery is REPEALED. A reserve breach shall NEVER trigger a capital call. Post-stabilisation capital calls are GROWTH capital only - never operating deficits, routine maintenance, or reserve replenishment.</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1272,22 +1234,22 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>BLANK-21</t>
+          <t>BLANK-23</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>L1-16 Part III</t>
+          <t>L1-01 §23</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Leverage limit</t>
+          <t>FINANCIAL invariant ID collision</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>RATIFIED - NO constitutional LTV, portfolio ratio or DSCR. Rationale: multiple LLPs with different asset classes, lenders and risk profiles; a fixed number would either go stale or force amendments. Limits set per LLP by the Investment Committee, documented in the Investment Memorandum and Financing Plan BEFORE debt is incurred. Once approved the limit is HARD for that LLP; exceeding it requires revised proposal + renewed IC recommendation + Special Resolution where investor risk materially changes. Asset-stage variation permitted and disclosed. Recourse vs non-recourse decided per transaction and disclosed before capital commitment. This is what makes the EP-01 §3.8 leverage trigger operable - previously it referenced limits that did not exist.</t>
+          <t>RATIFIED - MERGED. L1-01 §23 and L1-14 independently assigned the same F-identifiers to different rules, violating §14 Naming Authority. The two sets are merged into ONE canonical table of 18 in L1-01 §23, which is now the sole FINANCIAL numbering. Every rule from both survived; only numbers changed. L1-14 Part IV retains its prose but its numbers are VOID and carry an explicit old-to-new mapping table. Resolved before Wave 2 began, because Wave 2 bakes invariant ids into field definitions.</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1299,25 +1261,133 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>BLANK-09a</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>L1-16 §2.6a</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Reserve breach - does distribution suspension survive?</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>RATIFIED - TWO DISTINCT TESTS. (1) PROSPECTIVE: a distribution that would ITSELF take the reserve below floor is rejected automatically and is NOT voteable - a floor a single payment may cross at will is not a floor. (2) EXISTING BREACH: where the reserve is already below floor, scheduled distributions CONTINUE unless suspended by Ordinary Resolution (&gt;50% of equity present). Automatic on any breach: broadcast to Board, Executive Office and affected LLP Partners, plus deferral of discretionary expenditure. RECORDED TENSION accepted knowingly: partners voting on whether to pause their own distributions are voting on their own cash, and the incentive runs toward continuing to distribute from a vehicle already below its liquidity floor. Limited by the non-voteable prospective test, by the breach being broadcast so the decision is made in the open, and by expenditure deferral operating regardless. Residual exposure: a prolonged sub-floor period sustained by repeated small distributions each individually lawful. Reserve Coverage Ratio (UFR-0385) makes it visible; nothing else prevents it.</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>30 Jul 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>BLANK-26</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>WAVE-2-ARCHITECTURE-TARGET</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Status of GC.SYSTEM v3.0 Sovereign OS scaffold</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>RATIFIED - MIGRATION TARGET, not current state. C:/gc-app remains authoritative and nothing restructures now; an empty Turborepo would constrain L7/L8 decisions the semantic layer has not yet made. Palette reconciles with zero drift (10/10 verified programmatically). Tier 05 Financial Objects do NOT reconcile - none of Fund/Asset/Deal/Portfolio/Cash Flow/Covenant/Fraction is a canonical L2 name; mapping recorded, with Fraction the consequential one since it carries a retail fractional-ownership framing the constitution rejects. UI state COMMITTED renamed SEALED to avoid colliding with Commitment (UFR-0182). Eight-step migration sequence recorded; step 3 (generate Zod from the UFR rather than transcribing) is the one that keeps E-06 true.</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>30 Jul 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>BLANK-27</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>WAVE-2-ARCHITECTURE-TARGET §4</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>GC.SYSTEM vocabulary - canonicalise or exempt?</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>RATIFIED (delegated) - SPLIT BY DESTINATION, NOT CONTENT. System surface (routes, directories, components, types, schema fields, API contracts) MUST be canonical, because it becomes code and would put the linter permanently at war with the codebase: Steward Passport -&gt; Member Passport, EXP Physical Asset Space -&gt; AST Asset Space, PUB Seduction -&gt; PUB Public Root, Steward Investor -&gt; Investor/Member, Tier 05 names -&gt; the 27 canonical objects. The 8-Pillar brand strategy matrix sits OUTSIDE linter scope as an internal marketing-practice artifact whose pillar names never become tables, routes or fields; forcing it through would yield contortions that serve no engineer. CONDITION on the exemption: the framework stays out of packages/ and apps/. The moment a pillar name becomes a directory, component or field, the canonical rule applies to it.</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>30 Jul 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>BLANK-21</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>L1-16 Part III</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Leverage limit</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>RATIFIED - NO constitutional LTV, portfolio ratio or DSCR. Rationale: multiple LLPs with different asset classes, lenders and risk profiles; a fixed number would either go stale or force amendments. Limits set per LLP by the Investment Committee, documented in the Investment Memorandum and Financing Plan BEFORE debt is incurred. Once approved the limit is HARD for that LLP; exceeding it requires revised proposal + renewed IC recommendation + Special Resolution where investor risk materially changes. Asset-stage variation permitted and disclosed. Recourse vs non-recourse decided per transaction and disclosed before capital commitment. This is what makes the EP-01 §3.8 leverage trigger operable - previously it referenced limits that did not exist.</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>30 Jul 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
           <t>BLANK-22</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>L1-16 Parts I &amp; IV</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>Brand Co revenue participation formula</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>RATIFIED - Six-stage waterfall: (1) Operating Company (2) Brand &amp; Digital Company (3) Enterprise Admin Reserve 2.5% (4) Property Sinking Fund 2.5% (5) Debt Service (6) LLP Partner Distributions. NO preferred return, NO catch-up, NO carried interest - GC holds no equity so has no promote. REVENUE BASE defined constitutionally and REFINED 30 Jul: gross operating receipts less ONLY, in respect of a booking - statutory taxes; booking platform fees; channel/OTA commissions; payment settlement and processing charges; guest refunds and chargebacks. CRITICAL READING: "platform fee" means the BOOKING platform fee, NOT the GC Platform Administration Fee. No fee payable to GC or an affiliated division may be deducted in computing the Revenue Base - doing so would rank GC compensation ahead of both reserves, debt service and every partner distribution, and would shrink the base from which the Brand participation and both reserves are calculated. That is a fiduciary inversion and is prohibited. Brand rate is property-specific, set at underwriting, IC-approved, Board-ratified, disclosed in the Investment Memorandum, fixed for term. Participation is consideration for services - never dilutes ownership, never confers governance or voting rights. KPI-linked with Board remedies up to termination. Annual review. Board fairness benchmark required before approval or renewal.</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>30 Jul 2026</t>
         </is>
@@ -1360,14 +1430,14 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>OPEN: 2   (BLANK-23 F-invariant ID collision, BLANK-09a distribution-suspension confirmation)</t>
+          <t>OPEN: 1   (BLANK-25 - should Consumer join the forbidden list)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>RATIFIED: 26</t>
+          <t>RATIFIED: 30</t>
         </is>
       </c>
     </row>

--- a/L1-BLANKS-REGISTER.xlsx
+++ b/L1-BLANKS-REGISTER.xlsx
@@ -500,37 +500,37 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>BLANK-25</t>
+          <t>BLANK-28</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>L1-01 §25 Vocabulary</t>
+          <t>L1-16 Part I</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Should "Consumer" join the forbidden term list? It appears 6 times in GC.SYSTEM v3.0. Currently only Customer and User are forbidden, so the linter passes Consumer.</t>
+          <t>No cap on the Stage 1 Operating Company share, and no subordination of it to reserve funding. The ratified waterfall order is 1 OpCo, 2 Brand, 3 Admin Reserve, 4 Sinking Fund, 5 Debt Service, 6 Partners - so the Operating Company ranks AHEAD of both constitutional reserves AND debt service. Demonstrated in tests: a 90 percent operating share leaves the Admin Reserve short by 5,000, the Sinking Fund at zero and debt service wholly unpaid, on a 1,000,000 Revenue Base.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>PROPOSED: add it. Same family and same error as Customer - it frames a Member as someone who consumes rather than someone who owns. Adding it is a constitutional vocabulary amendment under §25 and is not mine to make unilaterally. One word closes this.</t>
+          <t>CANNOT DEFAULT - this is a commercial and fiduciary judgement. Three options: (a) accept as ratified, relying on the Operating Agreement to cap the share commercially rather than constitutionally; (b) cap the Stage 1 share at a constitutional ceiling expressed in basis points of Revenue Base; (c) subordinate Stage 1 to Stages 3-5, so reserves and debt service fund before the operator is paid. Option (c) is the institutional norm but materially changes the operator economics you have already modelled. The engine currently implements exactly what was ratified.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>L8 UX, brand surface</t>
+          <t>F-05, F-06, L1-16 Part I</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Knowledge Office</t>
+          <t>Executive Office + Finance</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -546,7 +546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1288,22 +1288,22 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>BLANK-26</t>
+          <t>BLANK-25</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>WAVE-2-ARCHITECTURE-TARGET</t>
+          <t>L1-01 §25 Vocabulary</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Status of GC.SYSTEM v3.0 Sovereign OS scaffold</t>
+          <t>Should Consumer join the forbidden list?</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>RATIFIED - MIGRATION TARGET, not current state. C:/gc-app remains authoritative and nothing restructures now; an empty Turborepo would constrain L7/L8 decisions the semantic layer has not yet made. Palette reconciles with zero drift (10/10 verified programmatically). Tier 05 Financial Objects do NOT reconcile - none of Fund/Asset/Deal/Portfolio/Cash Flow/Covenant/Fraction is a canonical L2 name; mapping recorded, with Fraction the consequential one since it carries a retail fractional-ownership framing the constitution rejects. UI state COMMITTED renamed SEALED to avoid colliding with Commitment (UFR-0182). Eight-step migration sequence recorded; step 3 (generate Zod from the UFR rather than transcribing) is the one that keeps E-06 true.</t>
+          <t>RATIFIED - YES. Getaway Collective has Investor and Member, not Consumer. A Member owns; they do not consume. Linter now enforces 16 terms; the codebase was already clean.</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1315,22 +1315,22 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>BLANK-27</t>
+          <t>BLANK-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>WAVE-2-ARCHITECTURE-TARGET §4</t>
+          <t>WAVE-2-ARCHITECTURE-TARGET</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>GC.SYSTEM vocabulary - canonicalise or exempt?</t>
+          <t>Status of GC.SYSTEM v3.0 Sovereign OS scaffold</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>RATIFIED (delegated) - SPLIT BY DESTINATION, NOT CONTENT. System surface (routes, directories, components, types, schema fields, API contracts) MUST be canonical, because it becomes code and would put the linter permanently at war with the codebase: Steward Passport -&gt; Member Passport, EXP Physical Asset Space -&gt; AST Asset Space, PUB Seduction -&gt; PUB Public Root, Steward Investor -&gt; Investor/Member, Tier 05 names -&gt; the 27 canonical objects. The 8-Pillar brand strategy matrix sits OUTSIDE linter scope as an internal marketing-practice artifact whose pillar names never become tables, routes or fields; forcing it through would yield contortions that serve no engineer. CONDITION on the exemption: the framework stays out of packages/ and apps/. The moment a pillar name becomes a directory, component or field, the canonical rule applies to it.</t>
+          <t>RATIFIED - MIGRATION TARGET, not current state. C:/gc-app remains authoritative and nothing restructures now; an empty Turborepo would constrain L7/L8 decisions the semantic layer has not yet made. Palette reconciles with zero drift (10/10 verified programmatically). Tier 05 Financial Objects do NOT reconcile - none of Fund/Asset/Deal/Portfolio/Cash Flow/Covenant/Fraction is a canonical L2 name; mapping recorded, with Fraction the consequential one since it carries a retail fractional-ownership framing the constitution rejects. UI state COMMITTED renamed SEALED to avoid colliding with Commitment (UFR-0182). Eight-step migration sequence recorded; step 3 (generate Zod from the UFR rather than transcribing) is the one that keeps E-06 true.</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1342,22 +1342,22 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>BLANK-21</t>
+          <t>BLANK-27</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>L1-16 Part III</t>
+          <t>WAVE-2-ARCHITECTURE-TARGET §4</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Leverage limit</t>
+          <t>GC.SYSTEM vocabulary - canonicalise or exempt?</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>RATIFIED - NO constitutional LTV, portfolio ratio or DSCR. Rationale: multiple LLPs with different asset classes, lenders and risk profiles; a fixed number would either go stale or force amendments. Limits set per LLP by the Investment Committee, documented in the Investment Memorandum and Financing Plan BEFORE debt is incurred. Once approved the limit is HARD for that LLP; exceeding it requires revised proposal + renewed IC recommendation + Special Resolution where investor risk materially changes. Asset-stage variation permitted and disclosed. Recourse vs non-recourse decided per transaction and disclosed before capital commitment. This is what makes the EP-01 §3.8 leverage trigger operable - previously it referenced limits that did not exist.</t>
+          <t>RATIFIED (delegated) - SPLIT BY DESTINATION, NOT CONTENT. System surface (routes, directories, components, types, schema fields, API contracts) MUST be canonical, because it becomes code and would put the linter permanently at war with the codebase: Steward Passport -&gt; Member Passport, EXP Physical Asset Space -&gt; AST Asset Space, PUB Seduction -&gt; PUB Public Root, Steward Investor -&gt; Investor/Member, Tier 05 names -&gt; the 27 canonical objects. The 8-Pillar brand strategy matrix sits OUTSIDE linter scope as an internal marketing-practice artifact whose pillar names never become tables, routes or fields; forcing it through would yield contortions that serve no engineer. CONDITION on the exemption: the framework stays out of packages/ and apps/. The moment a pillar name becomes a directory, component or field, the canonical rule applies to it.</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1369,25 +1369,52 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>BLANK-21</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>L1-16 Part III</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Leverage limit</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>RATIFIED - NO constitutional LTV, portfolio ratio or DSCR. Rationale: multiple LLPs with different asset classes, lenders and risk profiles; a fixed number would either go stale or force amendments. Limits set per LLP by the Investment Committee, documented in the Investment Memorandum and Financing Plan BEFORE debt is incurred. Once approved the limit is HARD for that LLP; exceeding it requires revised proposal + renewed IC recommendation + Special Resolution where investor risk materially changes. Asset-stage variation permitted and disclosed. Recourse vs non-recourse decided per transaction and disclosed before capital commitment. This is what makes the EP-01 §3.8 leverage trigger operable - previously it referenced limits that did not exist.</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>30 Jul 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
           <t>BLANK-22</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>L1-16 Parts I &amp; IV</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Brand Co revenue participation formula</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>RATIFIED - Six-stage waterfall: (1) Operating Company (2) Brand &amp; Digital Company (3) Enterprise Admin Reserve 2.5% (4) Property Sinking Fund 2.5% (5) Debt Service (6) LLP Partner Distributions. NO preferred return, NO catch-up, NO carried interest - GC holds no equity so has no promote. REVENUE BASE defined constitutionally and REFINED 30 Jul: gross operating receipts less ONLY, in respect of a booking - statutory taxes; booking platform fees; channel/OTA commissions; payment settlement and processing charges; guest refunds and chargebacks. CRITICAL READING: "platform fee" means the BOOKING platform fee, NOT the GC Platform Administration Fee. No fee payable to GC or an affiliated division may be deducted in computing the Revenue Base - doing so would rank GC compensation ahead of both reserves, debt service and every partner distribution, and would shrink the base from which the Brand participation and both reserves are calculated. That is a fiduciary inversion and is prohibited. Brand rate is property-specific, set at underwriting, IC-approved, Board-ratified, disclosed in the Investment Memorandum, fixed for term. Participation is consideration for services - never dilutes ownership, never confers governance or voting rights. KPI-linked with Board remedies up to termination. Annual review. Board fairness benchmark required before approval or renewal.</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>30 Jul 2026</t>
         </is>
@@ -1430,14 +1457,14 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>OPEN: 1   (BLANK-25 - should Consumer join the forbidden list)</t>
+          <t>OPEN: 1   (BLANK-28 - Operating Company share ranks ahead of reserves and debt service)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>RATIFIED: 30</t>
+          <t>RATIFIED: 31</t>
         </is>
       </c>
     </row>

--- a/L1-BLANKS-REGISTER.xlsx
+++ b/L1-BLANKS-REGISTER.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -497,44 +497,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>BLANK-28</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>L1-16 Part I</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>No cap on the Stage 1 Operating Company share, and no subordination of it to reserve funding. The ratified waterfall order is 1 OpCo, 2 Brand, 3 Admin Reserve, 4 Sinking Fund, 5 Debt Service, 6 Partners - so the Operating Company ranks AHEAD of both constitutional reserves AND debt service. Demonstrated in tests: a 90 percent operating share leaves the Admin Reserve short by 5,000, the Sinking Fund at zero and debt service wholly unpaid, on a 1,000,000 Revenue Base.</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>CANNOT DEFAULT - this is a commercial and fiduciary judgement. Three options: (a) accept as ratified, relying on the Operating Agreement to cap the share commercially rather than constitutionally; (b) cap the Stage 1 share at a constitutional ceiling expressed in basis points of Revenue Base; (c) subordinate Stage 1 to Stages 3-5, so reserves and debt service fund before the operator is paid. Option (c) is the institutional norm but materially changes the operator economics you have already modelled. The engine currently implements exactly what was ratified.</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>F-05, F-06, L1-16 Part I</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Executive Office + Finance</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -546,7 +508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1288,49 +1250,49 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>BLANK-25</t>
+          <t>BLANK-28</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>L1-01 §25 Vocabulary</t>
+          <t>L1-16 §1.1a</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Should Consumer join the forbidden list?</t>
+          <t>Operating Company ranks ahead of reserves and debt service</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>RATIFIED - YES. Getaway Collective has Investor and Member, not Consumer. A Member owns; they do not consume. Linter now enforces 16 terms; the codebase was already clean.</t>
+          <t>RATIFIED - ACCEPT AS ORDERED. Debt is owned by the Investment Vehicle; the Operating Company has nothing to do with it. The operator share is CONSIDERATION FOR SERVICES PERFORMED - the same economic class as the staff and utilities it pays out of that share - not a claim on profit. The Vehicle services its own borrowing, and funds its own reserve provisioning, out of what the property generates AFTER it has paid to be operated. Subordinating the operator to the Vehicle financing would ask a service provider to underwrite a debt it neither incurred nor benefits from. NO constitutional cap on the Stage 1 share: the share is a commercial term that varies by asset, and a fixed ceiling would go stale or force amendments. THE CONTROL ALREADY EXISTS ELSEWHERE - the Management Agreement is an ALWAYS-MATERIAL related-party transaction under EP-01 §4.10a, requiring Board approval to set and Board approval again to amend, regardless of value. The residual starvation risk is real, demonstrated in the test suite, and deliberately governed by the instrument rather than by a constitutional number.</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>30 Jul 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>BLANK-26</t>
+          <t>BLANK-25</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>WAVE-2-ARCHITECTURE-TARGET</t>
+          <t>L1-01 §25 Vocabulary</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Status of GC.SYSTEM v3.0 Sovereign OS scaffold</t>
+          <t>Should Consumer join the forbidden list?</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>RATIFIED - MIGRATION TARGET, not current state. C:/gc-app remains authoritative and nothing restructures now; an empty Turborepo would constrain L7/L8 decisions the semantic layer has not yet made. Palette reconciles with zero drift (10/10 verified programmatically). Tier 05 Financial Objects do NOT reconcile - none of Fund/Asset/Deal/Portfolio/Cash Flow/Covenant/Fraction is a canonical L2 name; mapping recorded, with Fraction the consequential one since it carries a retail fractional-ownership framing the constitution rejects. UI state COMMITTED renamed SEALED to avoid colliding with Commitment (UFR-0182). Eight-step migration sequence recorded; step 3 (generate Zod from the UFR rather than transcribing) is the one that keeps E-06 true.</t>
+          <t>RATIFIED - YES. Getaway Collective has Investor and Member, not Consumer. A Member owns; they do not consume. Linter now enforces 16 terms; the codebase was already clean.</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1342,22 +1304,22 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>BLANK-27</t>
+          <t>BLANK-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>WAVE-2-ARCHITECTURE-TARGET §4</t>
+          <t>WAVE-2-ARCHITECTURE-TARGET</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>GC.SYSTEM vocabulary - canonicalise or exempt?</t>
+          <t>Status of GC.SYSTEM v3.0 Sovereign OS scaffold</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>RATIFIED (delegated) - SPLIT BY DESTINATION, NOT CONTENT. System surface (routes, directories, components, types, schema fields, API contracts) MUST be canonical, because it becomes code and would put the linter permanently at war with the codebase: Steward Passport -&gt; Member Passport, EXP Physical Asset Space -&gt; AST Asset Space, PUB Seduction -&gt; PUB Public Root, Steward Investor -&gt; Investor/Member, Tier 05 names -&gt; the 27 canonical objects. The 8-Pillar brand strategy matrix sits OUTSIDE linter scope as an internal marketing-practice artifact whose pillar names never become tables, routes or fields; forcing it through would yield contortions that serve no engineer. CONDITION on the exemption: the framework stays out of packages/ and apps/. The moment a pillar name becomes a directory, component or field, the canonical rule applies to it.</t>
+          <t>RATIFIED - MIGRATION TARGET, not current state. C:/gc-app remains authoritative and nothing restructures now; an empty Turborepo would constrain L7/L8 decisions the semantic layer has not yet made. Palette reconciles with zero drift (10/10 verified programmatically). Tier 05 Financial Objects do NOT reconcile - none of Fund/Asset/Deal/Portfolio/Cash Flow/Covenant/Fraction is a canonical L2 name; mapping recorded, with Fraction the consequential one since it carries a retail fractional-ownership framing the constitution rejects. UI state COMMITTED renamed SEALED to avoid colliding with Commitment (UFR-0182). Eight-step migration sequence recorded; step 3 (generate Zod from the UFR rather than transcribing) is the one that keeps E-06 true.</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1369,22 +1331,22 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>BLANK-21</t>
+          <t>BLANK-27</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>L1-16 Part III</t>
+          <t>WAVE-2-ARCHITECTURE-TARGET §4</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Leverage limit</t>
+          <t>GC.SYSTEM vocabulary - canonicalise or exempt?</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>RATIFIED - NO constitutional LTV, portfolio ratio or DSCR. Rationale: multiple LLPs with different asset classes, lenders and risk profiles; a fixed number would either go stale or force amendments. Limits set per LLP by the Investment Committee, documented in the Investment Memorandum and Financing Plan BEFORE debt is incurred. Once approved the limit is HARD for that LLP; exceeding it requires revised proposal + renewed IC recommendation + Special Resolution where investor risk materially changes. Asset-stage variation permitted and disclosed. Recourse vs non-recourse decided per transaction and disclosed before capital commitment. This is what makes the EP-01 §3.8 leverage trigger operable - previously it referenced limits that did not exist.</t>
+          <t>RATIFIED (delegated) - SPLIT BY DESTINATION, NOT CONTENT. System surface (routes, directories, components, types, schema fields, API contracts) MUST be canonical, because it becomes code and would put the linter permanently at war with the codebase: Steward Passport -&gt; Member Passport, EXP Physical Asset Space -&gt; AST Asset Space, PUB Seduction -&gt; PUB Public Root, Steward Investor -&gt; Investor/Member, Tier 05 names -&gt; the 27 canonical objects. The 8-Pillar brand strategy matrix sits OUTSIDE linter scope as an internal marketing-practice artifact whose pillar names never become tables, routes or fields; forcing it through would yield contortions that serve no engineer. CONDITION on the exemption: the framework stays out of packages/ and apps/. The moment a pillar name becomes a directory, component or field, the canonical rule applies to it.</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1396,25 +1358,52 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>BLANK-21</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>L1-16 Part III</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Leverage limit</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>RATIFIED - NO constitutional LTV, portfolio ratio or DSCR. Rationale: multiple LLPs with different asset classes, lenders and risk profiles; a fixed number would either go stale or force amendments. Limits set per LLP by the Investment Committee, documented in the Investment Memorandum and Financing Plan BEFORE debt is incurred. Once approved the limit is HARD for that LLP; exceeding it requires revised proposal + renewed IC recommendation + Special Resolution where investor risk materially changes. Asset-stage variation permitted and disclosed. Recourse vs non-recourse decided per transaction and disclosed before capital commitment. This is what makes the EP-01 §3.8 leverage trigger operable - previously it referenced limits that did not exist.</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>30 Jul 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
           <t>BLANK-22</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>L1-16 Parts I &amp; IV</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>Brand Co revenue participation formula</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>RATIFIED - Six-stage waterfall: (1) Operating Company (2) Brand &amp; Digital Company (3) Enterprise Admin Reserve 2.5% (4) Property Sinking Fund 2.5% (5) Debt Service (6) LLP Partner Distributions. NO preferred return, NO catch-up, NO carried interest - GC holds no equity so has no promote. REVENUE BASE defined constitutionally and REFINED 30 Jul: gross operating receipts less ONLY, in respect of a booking - statutory taxes; booking platform fees; channel/OTA commissions; payment settlement and processing charges; guest refunds and chargebacks. CRITICAL READING: "platform fee" means the BOOKING platform fee, NOT the GC Platform Administration Fee. No fee payable to GC or an affiliated division may be deducted in computing the Revenue Base - doing so would rank GC compensation ahead of both reserves, debt service and every partner distribution, and would shrink the base from which the Brand participation and both reserves are calculated. That is a fiduciary inversion and is prohibited. Brand rate is property-specific, set at underwriting, IC-approved, Board-ratified, disclosed in the Investment Memorandum, fixed for term. Participation is consideration for services - never dilutes ownership, never confers governance or voting rights. KPI-linked with Board remedies up to termination. Annual review. Board fairness benchmark required before approval or renewal.</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>30 Jul 2026</t>
         </is>
@@ -1431,7 +1420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1457,14 +1446,14 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>OPEN: 1   (BLANK-28 - Operating Company share ranks ahead of reserves and debt service)</t>
+          <t>OPEN: 0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>RATIFIED: 31</t>
+          <t>RATIFIED: 32</t>
         </is>
       </c>
     </row>
@@ -1484,53 +1473,46 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>BLANK-23 is a DEFECT, not a decision. Two documents assign the same F-identifiers</t>
+          <t>All L1 blanks are ratified. Wave 2 has no open constitutional questions.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>to different rules. Must be fixed before any FINANCIAL invariant reaches code.</t>
-        </is>
-      </c>
+      <c r="A10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr"/>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>BLANK-09a is a one-line confirmation, not a design question.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>BLANK-09a is a one-line confirmation, not a design question.</t>
-        </is>
-      </c>
+      <c r="A12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr"/>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>AMENDED THIS SESSION (rulings that replaced earlier rulings):</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>AMENDED THIS SESSION (rulings that replaced earlier rulings):</t>
+          <t xml:space="preserve">  BLANK-09  breach response simplified - 5/15/30-day escalation repealed</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  BLANK-09  breach response simplified - 5/15/30-day escalation repealed</t>
+          <t xml:space="preserve">  BLANK-17  declaration authority - Governance &amp; Ethics Cmte -&gt; COO/CEO interim</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  BLANK-17  declaration authority - Governance &amp; Ethics Cmte -&gt; COO/CEO interim</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  BLANK-22  Revenue Base - booking platform fee and settlement charges added</t>
         </is>

--- a/L1-BLANKS-REGISTER.xlsx
+++ b/L1-BLANKS-REGISTER.xlsx
@@ -508,7 +508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1196,76 +1196,76 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>BLANK-23</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>L1-01 §23</t>
+          <t>L1-02 Part VII</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>FINANCIAL invariant ID collision</t>
+          <t>Brand voice conflict: Warm vs never persuades</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>RATIFIED - MERGED. L1-01 §23 and L1-14 independently assigned the same F-identifiers to different rules, violating §14 Naming Authority. The two sets are merged into ONE canonical table of 18 in L1-01 §23, which is now the sole FINANCIAL numbering. Every rule from both survived; only numbers changed. L1-14 Part IV retains its prose but its numbers are VOID and carry an explicit old-to-new mapping table. Resolved before Wave 2 began, because Wave 2 bakes invariant ids into field definitions.</t>
+          <t>RATIFIED 31 Jul 2026 - WARM, CONFIDENT, ASSERTIVE, WITH PLEASANTNESS. The two ratified documents were only in conflict because WARM was being read as SOFT. Warmth is about WHO we speak to - a person owed a plain answer. Persuasion is about WHAT WE WANT from them. A message can be warm and want nothing. Addendum A three principles survive inside the four: Sovereign and Unadorned are what CONFIDENT means in practice, Deterministic is what ASSERTIVE means. Intelligent, Unvarnished and Patient are absorbed; Collaborative retired because it made copy ask questions it did not intend to act on. Governs EVERY string the enterprise emits - there is no second voice for error states. All 25 validation messages rewritten. Enforced by scripts/voice-lint.js over 338 member-facing strings: no apology, no hedging, no blame, no softeners, no exclamation marks, and accessible text must name the field first.</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>30 Jul 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>BLANK-09a</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>L1-16 §2.6a</t>
+          <t>Addendum A RISK_COLOUR</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Reserve breach - does distribution suspension survive?</t>
+          <t>Risk categories: 8 in design system, 10 in registry</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>RATIFIED - TWO DISTINCT TESTS. (1) PROSPECTIVE: a distribution that would ITSELF take the reserve below floor is rejected automatically and is NOT voteable - a floor a single payment may cross at will is not a floor. (2) EXISTING BREACH: where the reserve is already below floor, scheduled distributions CONTINUE unless suspended by Ordinary Resolution (&gt;50% of equity present). Automatic on any breach: broadcast to Board, Executive Office and affected LLP Partners, plus deferral of discretionary expenditure. RECORDED TENSION accepted knowingly: partners voting on whether to pause their own distributions are voting on their own cash, and the incentive runs toward continuing to distribute from a vehicle already below its liquidity floor. Limited by the non-voteable prospective test, by the breach being broadcast so the decision is made in the open, and by expenditure deferral operating regardless. Residual exposure: a prolonged sub-floor period sustained by repeated small distributions each individually lawful. Reserve Coverage Ratio (UFR-0385) makes it visible; nothing else prevents it.</t>
+          <t>RATIFIED 31 Jul 2026 - ACCEPT ALL. Six of ten rendered grey, which makes a risk register unscannable, the one thing a register exists to be. Four design-only names mapped onto registry synonyms (operational to operator, compliance to regulatory); two reused (reputation purple to counterparty, construction copper to interest_rate - both logged as reuse rather than mapping); two new colours (currency #B8873F amber-gold, technology #5A7D9A slate blue). construction and reputation DROPPED - the registry does not track them and adding them would be a §32a amendment. All ten now distinct, nothing grey. A test caught that the fallback was #6B6B6B steel, identical to LEGAL risk, so an unmapped category impersonated a legal one; fallback moved to steelDim.</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>30 Jul 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>BLANK-28</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>L1-16 §1.1a</t>
+          <t>L1-01 §29 + §29-0</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Operating Company ranks ahead of reserves and debt service</t>
+          <t>Design system version: v3.0 locked vs v4.0 referenced</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>RATIFIED - ACCEPT AS ORDERED. Debt is owned by the Investment Vehicle; the Operating Company has nothing to do with it. The operator share is CONSIDERATION FOR SERVICES PERFORMED - the same economic class as the staff and utilities it pays out of that share - not a claim on profit. The Vehicle services its own borrowing, and funds its own reserve provisioning, out of what the property generates AFTER it has paid to be operated. Subordinating the operator to the Vehicle financing would ask a service provider to underwrite a debt it neither incurred nor benefits from. NO constitutional cap on the Stage 1 share: the share is a commercial term that varies by asset, and a fixed ceiling would go stale or force amendments. THE CONTROL ALREADY EXISTS ELSEWHERE - the Management Agreement is an ALWAYS-MATERIAL related-party transaction under EP-01 §4.10a, requiring Board approval to set and Board approval again to amend, regardless of value. The residual starvation risk is real, demonstrated in the test suite, and deliberately governed by the instrument rather than by a constitutional number.</t>
+          <t>RATIFIED 31 Jul 2026 - INTEGRATED. §29 amended to name GC.SYSTEM as THREE parts with fixed precedence: Core (canonical) then Addendum A (motion, overlays, notifications, brand, full-bleed) then the Accessibility extension (ground variants). Each later part may only ADD; none may alter a value declared by an earlier one. The clause is now VERSION-AGNOSTIC: it binds to GC.SYSTEM as constituted, not to a number. v4.0 ratified as successor to v3.0 after value-by-value verification showed ZERO DRIFT across 17 colours, 4 typefaces, 10 spacing steps, 2 curves and 4 durations. A version bump changing no value is not a constitutional event; one changing a value is a §32a amendment. New §29-0a makes accessibility part of the system rather than a review of it.</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1277,76 +1277,76 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>BLANK-25</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>L1-01 §25 Vocabulary</t>
+          <t>L1-01 §29-0a</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Should Consumer join the forbidden list?</t>
+          <t>Four contrast variants added to the palette</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>RATIFIED - YES. Getaway Collective has Investor and Member, not Consumer. A Member owns; they do not consume. Linter now enforces 16 terms; the codebase was already clean.</t>
+          <t>RATIFIED 31 Jul 2026 - SIGNED OFF. forestLight #228A68 (forest on void was 1.38:1, a dark green on near-black, effectively invisible), copperDeep #8C6635 (copper is the CURRENCY token and was 2.18:1 on paper), confirmDeep #177F43, hazardDeep #BE4915. Each holds its original hue and saturation and moves only lightness to the first value clearing 4.5:1. EVERY ORIGINAL TOKEN KEEPS ITS EXACT VALUE - additive, not a change, so §29 supremacy is intact. ON_GROUND makes the ground-specific choice once so it is not remembered everywhere.</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>30 Jul 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>BLANK-26</t>
+          <t>B3</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>WAVE-2-ARCHITECTURE-TARGET</t>
+          <t>lib/processes.ts</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Status of GC.SYSTEM v3.0 Sovereign OS scaffold</t>
+          <t>Process step expiry windows</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>RATIFIED - MIGRATION TARGET, not current state. C:/gc-app remains authoritative and nothing restructures now; an empty Turborepo would constrain L7/L8 decisions the semantic layer has not yet made. Palette reconciles with zero drift (10/10 verified programmatically). Tier 05 Financial Objects do NOT reconcile - none of Fund/Asset/Deal/Portfolio/Cash Flow/Covenant/Fraction is a canonical L2 name; mapping recorded, with Fraction the consequential one since it carries a retail fractional-ownership framing the constitution rejects. UI state COMMITTED renamed SEALED to avoid colliding with Commitment (UFR-0182). Eight-step migration sequence recorded; step 3 (generate Zod from the UFR rather than transcribing) is the one that keeps E-06 true.</t>
+          <t>RATIFIED 31 Jul 2026 - ALIGNED. Accreditation decision 15 working days (from §24b); diligence workstream 180 days; independent valuation 365 days (EP-01 §5.14 annual minimum); IC acquisition approval 90 days. The last was invented and is the tightest: a committee approved the asset AT A PRICE, and after a quarter that is a different decision. Accreditation EVIDENCE (steps A1-A5) holds indefinitely and resumes where it stopped - re-verifying an unchanged passport helps nobody. Only the DECISION expires.</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>30 Jul 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>BLANK-27</t>
+          <t>BLANK-23</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>WAVE-2-ARCHITECTURE-TARGET §4</t>
+          <t>L1-01 §23</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>GC.SYSTEM vocabulary - canonicalise or exempt?</t>
+          <t>FINANCIAL invariant ID collision</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>RATIFIED (delegated) - SPLIT BY DESTINATION, NOT CONTENT. System surface (routes, directories, components, types, schema fields, API contracts) MUST be canonical, because it becomes code and would put the linter permanently at war with the codebase: Steward Passport -&gt; Member Passport, EXP Physical Asset Space -&gt; AST Asset Space, PUB Seduction -&gt; PUB Public Root, Steward Investor -&gt; Investor/Member, Tier 05 names -&gt; the 27 canonical objects. The 8-Pillar brand strategy matrix sits OUTSIDE linter scope as an internal marketing-practice artifact whose pillar names never become tables, routes or fields; forcing it through would yield contortions that serve no engineer. CONDITION on the exemption: the framework stays out of packages/ and apps/. The moment a pillar name becomes a directory, component or field, the canonical rule applies to it.</t>
+          <t>RATIFIED - MERGED. L1-01 §23 and L1-14 independently assigned the same F-identifiers to different rules, violating §14 Naming Authority. The two sets are merged into ONE canonical table of 18 in L1-01 §23, which is now the sole FINANCIAL numbering. Every rule from both survived; only numbers changed. L1-14 Part IV retains its prose but its numbers are VOID and carry an explicit old-to-new mapping table. Resolved before Wave 2 began, because Wave 2 bakes invariant ids into field definitions.</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1358,22 +1358,22 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>BLANK-21</t>
+          <t>BLANK-09a</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>L1-16 Part III</t>
+          <t>L1-16 §2.6a</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Leverage limit</t>
+          <t>Reserve breach - does distribution suspension survive?</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>RATIFIED - NO constitutional LTV, portfolio ratio or DSCR. Rationale: multiple LLPs with different asset classes, lenders and risk profiles; a fixed number would either go stale or force amendments. Limits set per LLP by the Investment Committee, documented in the Investment Memorandum and Financing Plan BEFORE debt is incurred. Once approved the limit is HARD for that LLP; exceeding it requires revised proposal + renewed IC recommendation + Special Resolution where investor risk materially changes. Asset-stage variation permitted and disclosed. Recourse vs non-recourse decided per transaction and disclosed before capital commitment. This is what makes the EP-01 §3.8 leverage trigger operable - previously it referenced limits that did not exist.</t>
+          <t>RATIFIED - TWO DISTINCT TESTS. (1) PROSPECTIVE: a distribution that would ITSELF take the reserve below floor is rejected automatically and is NOT voteable - a floor a single payment may cross at will is not a floor. (2) EXISTING BREACH: where the reserve is already below floor, scheduled distributions CONTINUE unless suspended by Ordinary Resolution (&gt;50% of equity present). Automatic on any breach: broadcast to Board, Executive Office and affected LLP Partners, plus deferral of discretionary expenditure. RECORDED TENSION accepted knowingly: partners voting on whether to pause their own distributions are voting on their own cash, and the incentive runs toward continuing to distribute from a vehicle already below its liquidity floor. Limited by the non-voteable prospective test, by the breach being broadcast so the decision is made in the open, and by expenditure deferral operating regardless. Residual exposure: a prolonged sub-floor period sustained by repeated small distributions each individually lawful. Reserve Coverage Ratio (UFR-0385) makes it visible; nothing else prevents it.</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1385,25 +1385,160 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>BLANK-28</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>L1-16 §1.1a</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Operating Company ranks ahead of reserves and debt service</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>RATIFIED - ACCEPT AS ORDERED. Debt is owned by the Investment Vehicle; the Operating Company has nothing to do with it. The operator share is CONSIDERATION FOR SERVICES PERFORMED - the same economic class as the staff and utilities it pays out of that share - not a claim on profit. The Vehicle services its own borrowing, and funds its own reserve provisioning, out of what the property generates AFTER it has paid to be operated. Subordinating the operator to the Vehicle financing would ask a service provider to underwrite a debt it neither incurred nor benefits from. NO constitutional cap on the Stage 1 share: the share is a commercial term that varies by asset, and a fixed ceiling would go stale or force amendments. THE CONTROL ALREADY EXISTS ELSEWHERE - the Management Agreement is an ALWAYS-MATERIAL related-party transaction under EP-01 §4.10a, requiring Board approval to set and Board approval again to amend, regardless of value. The residual starvation risk is real, demonstrated in the test suite, and deliberately governed by the instrument rather than by a constitutional number.</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>31 Jul 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>BLANK-25</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>L1-01 §25 Vocabulary</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Should Consumer join the forbidden list?</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>RATIFIED - YES. Getaway Collective has Investor and Member, not Consumer. A Member owns; they do not consume. Linter now enforces 16 terms; the codebase was already clean.</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>30 Jul 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>BLANK-26</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>WAVE-2-ARCHITECTURE-TARGET</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Status of GC.SYSTEM v3.0 Sovereign OS scaffold</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>RATIFIED - MIGRATION TARGET, not current state. C:/gc-app remains authoritative and nothing restructures now; an empty Turborepo would constrain L7/L8 decisions the semantic layer has not yet made. Palette reconciles with zero drift (10/10 verified programmatically). Tier 05 Financial Objects do NOT reconcile - none of Fund/Asset/Deal/Portfolio/Cash Flow/Covenant/Fraction is a canonical L2 name; mapping recorded, with Fraction the consequential one since it carries a retail fractional-ownership framing the constitution rejects. UI state COMMITTED renamed SEALED to avoid colliding with Commitment (UFR-0182). Eight-step migration sequence recorded; step 3 (generate Zod from the UFR rather than transcribing) is the one that keeps E-06 true.</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>30 Jul 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>BLANK-27</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>WAVE-2-ARCHITECTURE-TARGET §4</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>GC.SYSTEM vocabulary - canonicalise or exempt?</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>RATIFIED (delegated) - SPLIT BY DESTINATION, NOT CONTENT. System surface (routes, directories, components, types, schema fields, API contracts) MUST be canonical, because it becomes code and would put the linter permanently at war with the codebase: Steward Passport -&gt; Member Passport, EXP Physical Asset Space -&gt; AST Asset Space, PUB Seduction -&gt; PUB Public Root, Steward Investor -&gt; Investor/Member, Tier 05 names -&gt; the 27 canonical objects. The 8-Pillar brand strategy matrix sits OUTSIDE linter scope as an internal marketing-practice artifact whose pillar names never become tables, routes or fields; forcing it through would yield contortions that serve no engineer. CONDITION on the exemption: the framework stays out of packages/ and apps/. The moment a pillar name becomes a directory, component or field, the canonical rule applies to it.</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>30 Jul 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>BLANK-21</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>L1-16 Part III</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Leverage limit</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>RATIFIED - NO constitutional LTV, portfolio ratio or DSCR. Rationale: multiple LLPs with different asset classes, lenders and risk profiles; a fixed number would either go stale or force amendments. Limits set per LLP by the Investment Committee, documented in the Investment Memorandum and Financing Plan BEFORE debt is incurred. Once approved the limit is HARD for that LLP; exceeding it requires revised proposal + renewed IC recommendation + Special Resolution where investor risk materially changes. Asset-stage variation permitted and disclosed. Recourse vs non-recourse decided per transaction and disclosed before capital commitment. This is what makes the EP-01 §3.8 leverage trigger operable - previously it referenced limits that did not exist.</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>30 Jul 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
           <t>BLANK-22</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>L1-16 Parts I &amp; IV</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>Brand Co revenue participation formula</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>RATIFIED - Six-stage waterfall: (1) Operating Company (2) Brand &amp; Digital Company (3) Enterprise Admin Reserve 2.5% (4) Property Sinking Fund 2.5% (5) Debt Service (6) LLP Partner Distributions. NO preferred return, NO catch-up, NO carried interest - GC holds no equity so has no promote. REVENUE BASE defined constitutionally and REFINED 30 Jul: gross operating receipts less ONLY, in respect of a booking - statutory taxes; booking platform fees; channel/OTA commissions; payment settlement and processing charges; guest refunds and chargebacks. CRITICAL READING: "platform fee" means the BOOKING platform fee, NOT the GC Platform Administration Fee. No fee payable to GC or an affiliated division may be deducted in computing the Revenue Base - doing so would rank GC compensation ahead of both reserves, debt service and every partner distribution, and would shrink the base from which the Brand participation and both reserves are calculated. That is a fiduciary inversion and is prohibited. Brand rate is property-specific, set at underwriting, IC-approved, Board-ratified, disclosed in the Investment Memorandum, fixed for term. Participation is consideration for services - never dilutes ownership, never confers governance or voting rights. KPI-linked with Board remedies up to termination. Annual review. Board fairness benchmark required before approval or renewal.</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>30 Jul 2026</t>
         </is>
@@ -1446,14 +1581,14 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>OPEN: 0</t>
+          <t>OPEN: 0   (Waves 1-5 fully ratified)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>RATIFIED: 32</t>
+          <t>RATIFIED: 37</t>
         </is>
       </c>
     </row>
